--- a/output/change-management/claude/sample-2/workpaper.xlsx
+++ b/output/change-management/claude/sample-2/workpaper.xlsx
@@ -1456,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:12:58.357525Z</t>
+          <t>2026-07-03T03:34:53.966142Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1537,19 +1537,19 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>4031</v>
+        <v>12210</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>1200</v>
+        <v>4050</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.114852</v>
+        <v>0.4869</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>14479</v>
+        <v>16818</v>
       </c>
     </row>
     <row r="3">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:13:13.294464Z</t>
+          <t>2026-07-03T03:35:39.656943Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-prior-to-deployment:sample-1</t>
+          <t>judge:approved-by-authorised-approver-pre-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -1572,185 +1572,45 @@
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>4107</v>
+        <v>12426</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>1180</v>
+        <v>3666</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.114492</v>
+        <v>0.46134</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>14933</v>
+        <v>15463</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:27.897046Z</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>judge:pre-deployment-testing-evidence-retained:sample-1</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>4077</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>1221</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.117117</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>14599</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:41.440103Z</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>judge:change-request-documents-scope-risk-rollback:sample-2</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>3888</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.106782</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>13531</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:55.701453Z</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>judge:authorised-approver-prior-to-deployment:sample-2</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>3964</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>1057</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.103122</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>14259</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:09.625203Z</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>judge:pre-deployment-testing-evidence-retained:sample-2</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>3934</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1141</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.108972</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>13920</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E8" s="20">
-        <f>SUM(E2:E7)</f>
+      <c r="E4" s="20">
+        <f>SUM(E2:E3)</f>
         <v/>
       </c>
-      <c r="F8" s="20">
-        <f>SUM(F2:F7)</f>
+      <c r="F4" s="20">
+        <f>SUM(F2:F3)</f>
         <v/>
       </c>
-      <c r="G8" s="20">
-        <f>SUM(G2:G7)</f>
+      <c r="G4" s="20">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
-      <c r="H8" s="21">
-        <f>SUM(H2:H7)</f>
+      <c r="H4" s="21">
+        <f>SUM(H2:H3)</f>
         <v/>
       </c>
-      <c r="I8" s="20">
-        <f>SUM(I2:I7)</f>
+      <c r="I4" s="20">
+        <f>SUM(I2:I3)</f>
         <v/>
       </c>
     </row>

--- a/output/change-management/claude/sample-2/workpaper.xlsx
+++ b/output/change-management/claude/sample-2/workpaper.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:14 UTC</t>
+          <t>03 Jul 2026, 03:49 UTC</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Remediate the root cause of the FAIL on “Production changes are approved by an authorised change approver prior to deployment”, then re-submit for testing. Rationale: The change is self-approved: requester and approver are both Marcus Bell, violating the four-eyes principle.</t>
+          <t>Remediate the root cause of the FAIL on “Production changes are approved by an authorised change approver prior to deployment”, then re-submit for testing. Rationale: The change is classified Normal, which requires 2 approvers (Change Coordinator + CAB Change Approver) and evidenced CAB review.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Remediate the root cause of the FAIL on “Pre-deployment testing is completed and evidence retained before release”, then re-submit for testing. Rationale: This is a Normal change with failed pre-deployment tests, yet deployment proceeded.</t>
+          <t>Remediate the root cause of the FAIL on “Pre-deployment testing is completed and evidence retained before release”, then re-submit for testing. Rationale: This is a Normal change.</t>
         </is>
       </c>
     </row>
@@ -901,16 +901,17 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>The change request exists with identifier CHG-2026-0912 (correct format), documents scope (systems, repositories, config surfaces), risk classification (Medium), a rollback plan with steps and RTO, a named requester and named approver, a planned window (2026-06-28 15:00–17:00 UTC), and categorises the change as Normal. All documentation-completeness criteria for this attribute are met. Note: the requester and approver being the same person is a separate approval/independence attribute and is not judged here.</t>
+          <t>The change request CHG-2026-0912 exists and follows the CHG-YYYY-NNNN format. It documents scope (systems affected: reports-api/worker/db; repositories: reports-service PR #47, infra-terraform PR #2438), risk classification (Medium), rollback plan (3 steps with 5-min RTO), a named requester and named approver (both Marcus Bell — note: independence is a separate attribute), planned window (2026-06-28 15:00–17:00 UTC), and category (Normal). The change is a new production service deployment, not an out-of-scope exception. All documentation-completeness criteria for this attribute are met.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only change exception — rejected: this deploys a new production service and RDS instance, not documentation.
-Dev/staging exception — rejected: deployment targets production per deployment-log.txt.</t>
+          <t>Documentation-only exception: rejected — deployment provisions new production services and RDS instance.
+Dev/staging exception: rejected — deployment log shows production ECS/RDS resources.
+Incident Response break-fix: rejected — CR is categorised Normal for an end-of-quarter feature launch, not an IR hotfix.</t>
         </is>
       </c>
     </row>
@@ -926,11 +927,11 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The change is self-approved: requester and approver are both Marcus Bell, violating the four-eyes principle. Additionally, this is a Normal change which requires 2 approvers (Change Coordinator + CAB Approver) with CAB review evidenced — the record explicitly states CAB was skipped and only a retroactive CAB was scheduled. Retrospective approval is only valid for Emergency changes, but this change is documented as Normal.</t>
+          <t>The change is classified Normal, which requires 2 approvers (Change Coordinator + CAB Change Approver) and evidenced CAB review. The change request records only a self-approval by Marcus Bell, who is also the requester — this violates the four-eyes principle. CAB review was explicitly skipped ("standing team autonomy waiver") and only scheduled retroactively; retrospective approval is only valid for Emergency changes per policy. Multiple criteria fail: same-person approver, single approver on a Normal change, and no CAB evidence.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
@@ -938,8 +939,8 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Considered whether a 'standing team autonomy waiver' could substitute for CAB approval — rejected, no such exception exists in the Change Management Policy.
-Considered whether retrospective CAB could cure the deficiency — rejected because retrospective approvals per policy are only valid for Emergency changes, and this is documented as Normal.</t>
+          <t>Retrospective/Emergency exception: rejected — the change is classified Normal, not Emergency, so the retrospective-CAB pathway does not apply.
+Documentation-only exception: rejected — this is a production service deployment with new infra.</t>
         </is>
       </c>
     </row>
@@ -955,20 +956,20 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>This is a Normal change with failed pre-deployment tests, yet deployment proceeded. Test Cases sheet shows TC-002 (Functional) and TC-004 (Regression) with Result=FAIL on 2026-06-28 09:02–09:06, and the change request itself acknowledges "3 test cases failed on staging... Deployment proceeded pending post-deployment fix". The deployment log confirms deployment completed at 15:31:02 UTC with status DEPLOYED. Per policy, "Failed tests block deployment for Standard/Normal changes" — this criterion is directly violated.</t>
+          <t>This is a Normal change. A test plan and results workbook is attached and dated 2026-06-28 09:02–09:06 UTC, prior to the 15:04 UTC deployment — so those criteria are met. However, the Test Cases sheet shows two functional tests (TC-002) and one regression test (TC-004) with Result=FAIL, and the change request itself acknowledges "3 test cases failed on staging ... Deployment proceeded pending post-deployment fix." Policy states "Failed tests block deployment for Standard/Normal changes" — deployment proceeded anyway (deployment-log confirms DEPLOYED status), directly contradicting the criterion "if any tests failed, deployment did not proceed."</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Emergency post-deployment testing allowance — rejected because the change request explicitly classifies this as Normal, not Emergency.
-Documentation-only exception — rejected; this deploys new services and infrastructure.</t>
+          <t>Emergency-change accepted-risk exception: rejected because the change request explicitly classifies this as Category=Normal, not Emergency, so the 'accepted risk' carve-out for failed tests does not apply.
+Documentation-only / dev-or-staging scope exception: rejected — this deploys a new production service (reports-api, reports-worker, reports-db).</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1033,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Change request identifier 'CHG-2026-0912' matches CHG-YYYY-NNNN format.</t>
+          <t>Change request identifier CHG-2026-0912 in required CHG-YYYY-NNNN format, titled 'Deploy new Q2 reporting service to production'.</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1050,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Header block (Category, Risk, System(s) affected, Repositories touched, Planned window)</t>
+          <t>Header block (Category/Risk/Systems/Repositories/Planned window)</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Category: Normal; Risk: Medium; systems reports-api/reports-worker/reports-db listed; repositories northpeak/reports-service PR #47 and northpeak/infra-terraform PR #2438 listed; planned window 2026-06-28 15:00 UTC → 17:00 UTC.</t>
+          <t>Category: Normal; Risk: Medium; Systems: reports-api, reports-worker, reports-db; Repositories: northpeak/reports-service PR #47, northpeak/infra-terraform PR #2438; Planned window: 2026-06-28 15:00–17:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1077,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Documents scope: deploy reporting service, provision RDS, configure IAM roles and API gateway routes (config surfaces).</t>
+          <t>Scope enumerated: deploy reporting service, provision RDS, configure IAM/API gateway routes.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1099,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Three-step rollback plan with timings and 5-minute RTO documented.</t>
+          <t>Rollback plan with 3 numbered steps and 5-minute RTO documented.</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1121,29 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Named requester Marcus Bell and named approver Marcus Bell are both documented (independence is a separate attribute).</t>
+          <t>Requester: Marcus Bell; Approver: Marcus Bell (independence is out of scope for this attribute but noted).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Every production change has a corresponding change request that documents scope, risk classification, and rollback plan</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Requester and Approver sections</t>
+          <t>Header (system line)</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Both Requester and Approver are listed as 'Marcus Bell (Platform Engineer) — marcus.bell@northpeakfinancial.com' — same human.</t>
+          <t>Deployment targets production reports-api/worker/db — confirms this is a production change, not dev/staging or docs-only, so no exception applies.</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1160,12 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Category header</t>
+          <t>Category line</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Category is 'Normal' with Risk 'Medium'.</t>
+          <t>Category: Normal, Risk: Medium — triggers 2-approver + CAB requirements.</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1182,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Approval record section</t>
+          <t>Requester and Approver sections</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>'CAB meeting reference: (none — deployed under standing team autonomy waiver)', 'Approval decision: Self-approved', note states CAB skipped and retroactive CAB scheduled for 2026-07-02.</t>
+          <t>Both requester and approver are listed as 'Marcus Bell (Platform Engineer) — marcus.bell@northpeakfinancial.com' — same human, violating four-eyes.</t>
         </is>
       </c>
     </row>
@@ -1198,39 +1199,39 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>deployment-log.txt</t>
+          <t>change-request.md</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>approval verification line at 15:04:20 UTC</t>
+          <t>Approval record section</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Log records 'approved by marcus.bell at 2026-06-28T14:47:00Z (self-approved)' confirming self-approval was accepted by the deployment runner.</t>
+          <t>CAB meeting reference '(none — deployed under standing team autonomy waiver)'; Approval decision 'Self-approved'; note states CAB was skipped to hit demo deadline and retroactive CAB scheduled for 2026-07-02.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
+          <t>Production changes are approved by an authorised change approver prior to deployment</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Header — Category</t>
+          <t>Line 2026-06-28 15:04:20 UTC approval verification</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Change is classified Category: Normal, Risk: Medium.</t>
+          <t>Log confirms 'approved by marcus.bell at 2026-06-28T14:47:00Z (self-approved)' — deployment proceeded on a self-approval.</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1248,12 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Test Cases!D3 (TC-002 Result)</t>
+          <t>Test Cases!D2:D6 (Result column)</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>TC-002 functional test 'reports service returns Q2 aggregate correctly' Result = FAIL, executed 2026-06-28 09:03.</t>
+          <t>TC-002 (functional, Q2 aggregate) = FAIL and TC-004 (regression, CSV columns) = FAIL; executed 2026-06-28 09:03 and 09:05 UTC by test-bot.</t>
         </is>
       </c>
     </row>
@@ -1264,17 +1265,17 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-test-results.xlsx</t>
+          <t>change-request.md</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Test Cases!D5 (TC-004 Result)</t>
+          <t>## Testing evidence section</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>TC-004 regression test 'legacy report export CSV columns unchanged' Result = FAIL, executed 2026-06-28 09:05.</t>
+          <t>States '3 test cases failed on staging (2 functional, 1 performance). Deployment proceeded pending post-deployment fix.'</t>
         </is>
       </c>
     </row>
@@ -1286,17 +1287,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Testing evidence section</t>
+          <t>Final line 2026-06-28 15:31:02 UTC</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Requester notes: '3 test cases failed on staging (2 functional, 1 performance). Deployment proceeded pending post-deployment fix.'</t>
+          <t>'CHG-2026-0912 complete — status: DEPLOYED (with known post-deploy defects to be fixed 2026-06-29)' — confirms deployment proceeded despite failed pre-deployment tests.</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1309,17 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>deployment-log.txt</t>
+          <t>pre-deployment-test-results.xlsx</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Final line — status</t>
+          <t>Test Cases!F2:F6 (Executed At)</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>Deployment completed 2026-06-28 15:31:02 UTC — 'status: DEPLOYED (with known post-deploy defects to be fixed 2026-06-29)', confirming release proceeded despite failed tests.</t>
+          <t>All test executions dated 2026-06-28 09:02–09:06 UTC, i.e. before deployment window start of 15:04 UTC — dating criterion met.</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1392,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, authorised-approver-prior-to-deployment, authorised-approver-prior-to-deployment, authorised-approver-prior-to-deployment, pre-deployment-testing-evidence-retained, pre-deployment-testing-evidence-retained</t>
+          <t>change-request-documented, change-request-documented, change-request-documented, change-request-documented, change-request-documented, authorised-approver-pre-deployment, authorised-approver-pre-deployment, authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1417,7 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>authorised-approver-prior-to-deployment, pre-deployment-testing-evidence-retained</t>
+          <t>change-request-documented, authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-testing-evidence-retained, pre-deployment-testing-evidence-retained</t>
+          <t>pre-deployment-testing-evidence, pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1523,12 +1524,12 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:34:53.966142Z</t>
+          <t>2026-07-03T03:40:38.512115Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documents-scope-risk-rollback:sample-1</t>
+          <t>judge:change-request-documented:sample-1</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
@@ -1537,19 +1538,19 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>12210</v>
+        <v>12237</v>
       </c>
       <c r="F2" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>4050</v>
+        <v>3945</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.4869</v>
+        <v>0.47943</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>16818</v>
+        <v>16903</v>
       </c>
     </row>
     <row r="3">
@@ -1558,12 +1559,12 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:39.656943Z</t>
+          <t>2026-07-03T03:41:38.676590Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:approved-by-authorised-approver-pre-deployment:sample-1</t>
+          <t>judge:authorised-approver-pre-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -1572,45 +1573,185 @@
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>12426</v>
+        <v>12282</v>
       </c>
       <c r="F3" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>3666</v>
+        <v>3635</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.46134</v>
+        <v>0.456855</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>15463</v>
+        <v>15711</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="20" t="inlineStr">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:42:20.425037Z</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>judge:pre-deployment-testing-evidence:sample-1</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>12171</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>3288</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>0.429165</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>14789</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:43:34.856033Z</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>judge:change-request-documented:sample-2</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>11808</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>3732</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>16764</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:44:17.557054Z</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>judge:authorised-approver-pre-deployment:sample-2</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>11853</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>3339</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>16002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:49:13.305734Z</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>judge:pre-deployment-testing-evidence:sample-2</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>11742</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>3528</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>264910</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E4" s="20">
-        <f>SUM(E2:E3)</f>
+      <c r="E8" s="20">
+        <f>SUM(E2:E7)</f>
         <v/>
       </c>
-      <c r="F4" s="20">
-        <f>SUM(F2:F3)</f>
+      <c r="F8" s="20">
+        <f>SUM(F2:F7)</f>
         <v/>
       </c>
-      <c r="G4" s="20">
-        <f>SUM(G2:G3)</f>
+      <c r="G8" s="20">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
-      <c r="H4" s="21">
-        <f>SUM(H2:H3)</f>
+      <c r="H8" s="21">
+        <f>SUM(H2:H7)</f>
         <v/>
       </c>
-      <c r="I4" s="20">
-        <f>SUM(I2:I3)</f>
+      <c r="I8" s="20">
+        <f>SUM(I2:I7)</f>
         <v/>
       </c>
     </row>

--- a/output/change-management/claude/sample-2/workpaper.xlsx
+++ b/output/change-management/claude/sample-2/workpaper.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:49 UTC</t>
+          <t>03 Jul 2026, 04:16 UTC</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Remediate the root cause of the FAIL on “Production changes are approved by an authorised change approver prior to deployment”, then re-submit for testing. Rationale: The change is classified Normal, which requires 2 approvers (Change Coordinator + CAB Change Approver) and evidenced CAB review.</t>
+          <t>Remediate the root cause of the FAIL on “Production changes are approved by an authorised change approver prior to deployment”, then re-submit for testing. Rationale: This is a Normal change (per the change request), which requires 2 approvers (Change Coordinator + CAB Change Approver) and CAB approval — instead it was self-approved by the requester Marcus Bell with no CAB review, violating the four-eyes principle.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Remediate the root cause of the FAIL on “Pre-deployment testing is completed and evidence retained before release”, then re-submit for testing. Rationale: This is a Normal change.</t>
+          <t>Remediate the root cause of the FAIL on “Pre-deployment testing is completed and evidence retained before release”, then re-submit for testing. Rationale: This is a Normal change (per change-request.</t>
         </is>
       </c>
     </row>
@@ -897,21 +897,20 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>The change request CHG-2026-0912 exists and follows the CHG-YYYY-NNNN format. It documents scope (systems affected: reports-api/worker/db; repositories: reports-service PR #47, infra-terraform PR #2438), risk classification (Medium), rollback plan (3 steps with 5-min RTO), a named requester and named approver (both Marcus Bell — note: independence is a separate attribute), planned window (2026-06-28 15:00–17:00 UTC), and category (Normal). The change is a new production service deployment, not an out-of-scope exception. All documentation-completeness criteria for this attribute are met.</t>
+          <t>A change request exists (CHG-2026-0912, correct CHG-YYYY-NNNN format) and documents scope (systems affected, repositories touched, config surfaces), a Medium risk classification, a rollback plan with RTO, a named requester, a named approver, and a planned window with start/end times. The change is in scope — it deploys new production services (reports-api/worker/db), not a documentation-only, incident-response hotfix, or dev/staging change. Note: the requester and approver are the same person (Marcus Bell), which violates four-eyes, but that is a separate approval-independence attribute and does not defeat this documentation-completeness attribute.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only exception: rejected — deployment provisions new production services and RDS instance.
-Dev/staging exception: rejected — deployment log shows production ECS/RDS resources.
-Incident Response break-fix: rejected — CR is categorised Normal for an end-of-quarter feature launch, not an IR hotfix.</t>
+          <t>Documentation-only / incident-response hotfix / dev-staging exception rejected — evidence shows a production deployment of new services (reports-api, reports-worker, RDS reports-db), so the change is in scope.
+Same-person requester and approver noted, but this is an approval-independence concern belonging to a separate attribute; per attribute isolation it does not fail this documentation-completeness attribute, which requires only that requester and approver be named (both are).</t>
         </is>
       </c>
     </row>
@@ -927,20 +926,20 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The change is classified Normal, which requires 2 approvers (Change Coordinator + CAB Change Approver) and evidenced CAB review. The change request records only a self-approval by Marcus Bell, who is also the requester — this violates the four-eyes principle. CAB review was explicitly skipped ("standing team autonomy waiver") and only scheduled retroactively; retrospective approval is only valid for Emergency changes per policy. Multiple criteria fail: same-person approver, single approver on a Normal change, and no CAB evidence.</t>
+          <t>This is a Normal change (per the change request), which requires 2 approvers (Change Coordinator + CAB Change Approver) and CAB approval — instead it was self-approved by the requester Marcus Bell with no CAB review, violating the four-eyes principle. The approver and requester are the same named human (marcus.bell), and the note explicitly states "skipped CAB review to hit end-of-quarter demo deadline." Retrospective approval is only valid for Emergency changes, but this is classified Normal, so the retroactive CAB scheduled for 2026-07-02 does not cure the defect. Multiple criteria fail.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Retrospective/Emergency exception: rejected — the change is classified Normal, not Emergency, so the retrospective-CAB pathway does not apply.
-Documentation-only exception: rejected — this is a production service deployment with new infra.</t>
+          <t>Retrospective approval exception — rejected: retrospective approvals are only valid for Emergency changes, but this change is classified Normal, so the retroactive CAB does not validate it.
+Standard-change single-approver path — rejected: the change request explicitly classifies this as a Normal change requiring 2 approvers plus CAB.</t>
         </is>
       </c>
     </row>
@@ -960,16 +959,16 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>This is a Normal change. A test plan and results workbook is attached and dated 2026-06-28 09:02–09:06 UTC, prior to the 15:04 UTC deployment — so those criteria are met. However, the Test Cases sheet shows two functional tests (TC-002) and one regression test (TC-004) with Result=FAIL, and the change request itself acknowledges "3 test cases failed on staging ... Deployment proceeded pending post-deployment fix." Policy states "Failed tests block deployment for Standard/Normal changes" — deployment proceeded anyway (deployment-log confirms DEPLOYED status), directly contradicting the criterion "if any tests failed, deployment did not proceed."</t>
+          <t>This is a Normal change (per change-request.md), so failed tests must block deployment. The pre-deployment test results show TC-002 (functional) and TC-004 (regression) both FAIL, and the change request itself admits "3 test cases failed on staging... Deployment proceeded pending post-deployment fix." The deployment log further shows two canary transactions FAILED (5xx) yet an override was applied ("accepting canary failure for demo") and the change completed as DEPLOYED. The criterion "IF Standard or Normal AND tests failed THEN was deployment blocked?" is positively contradicted — tests failed and deployment was not blocked.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Emergency-change accepted-risk exception: rejected because the change request explicitly classifies this as Category=Normal, not Emergency, so the 'accepted risk' carve-out for failed tests does not apply.
-Documentation-only / dev-or-staging scope exception: rejected — this deploys a new production service (reports-api, reports-worker, reports-db).</t>
+          <t>Documentation-only / staging-only exceptions rejected — this deploys new production services (reports-api, reports-worker, reports-db) to production, so no exception applies.
+Emergency post-deployment verification path rejected — change is explicitly categorized 'Normal', not Emergency, so the deployment-blocking rule (not the 24-hour verification rule) governs.</t>
         </is>
       </c>
     </row>
@@ -984,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1028,12 +1027,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Title line</t>
+          <t>Title + header block (CHG-2026-0912, Category/Risk/System(s) affected/Repositories touched/Planned window)</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Change request identifier CHG-2026-0912 in required CHG-YYYY-NNNN format, titled 'Deploy new Q2 reporting service to production'.</t>
+          <t>Identifier CHG-2026-0912 in CHG-YYYY-NNNN format; Risk: Medium; systems reports-api/reports-worker/reports-db; repos northpeak/reports-service PR#47 and infra-terraform PR#2438; planned window 2026-06-28 15:00→17:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1049,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Header block (Category/Risk/Systems/Repositories/Planned window)</t>
+          <t>## Scope and ## Rollback plan sections</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Category: Normal; Risk: Medium; Systems: reports-api, reports-worker, reports-db; Repositories: northpeak/reports-service PR #47, northpeak/infra-terraform PR #2438; Planned window: 2026-06-28 15:00–17:00 UTC.</t>
+          <t>Scope lists deploying reporting service, provisioning RDS, configuring IAM/API gateway routes. Rollback plan enumerates 3 steps with a 5-minute RTO.</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1071,12 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Scope section</t>
+          <t>## Requester and ## Approver sections</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Scope enumerated: deploy reporting service, provision RDS, configure IAM/API gateway routes.</t>
+          <t>Requester named as Marcus Bell (Platform Engineer); Approver also named as Marcus Bell — same person, satisfying the 'names requester/approver' criteria though not independence.</t>
         </is>
       </c>
     </row>
@@ -1089,24 +1088,24 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Rollback plan section</t>
+          <t>Header + provisioning/deploy lines</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Rollback plan with 3 numbered steps and 5-minute RTO documented.</t>
+          <t>Confirms this is a production deployment of new services (reports-api ECS rev 4, reports-worker, reports-db RDS), establishing the change is in scope for change management.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Every production change has a corresponding change request that documents scope, risk classification, and rollback plan</t>
+          <t>Production changes are approved by an authorised change approver prior to deployment</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -1116,34 +1115,34 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Requester and Approver sections</t>
+          <t>Category / Requester / Approver fields</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Requester: Marcus Bell; Approver: Marcus Bell (independence is out of scope for this attribute but noted).</t>
+          <t>Category is 'Normal'; both Requester and Approver are listed as the same person, Marcus Bell (marcus.bell@northpeakfinancial.com).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Every production change has a corresponding change request that documents scope, risk classification, and rollback plan</t>
+          <t>Production changes are approved by an authorised change approver prior to deployment</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>deployment-log.txt</t>
+          <t>change-request.md</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Header (system line)</t>
+          <t>Approval record section</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Deployment targets production reports-api/worker/db — confirms this is a production change, not dev/staging or docs-only, so no exception applies.</t>
+          <t>CAB meeting reference is '(none — deployed under standing team autonomy waiver)', decision is 'Self-approved', with a note that CAB review was skipped to hit an end-of-quarter deadline and a retroactive CAB scheduled for 2026-07-02.</t>
         </is>
       </c>
     </row>
@@ -1155,24 +1154,24 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Category line</t>
+          <t>approval verification line at 15:04:20 UTC</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Category: Normal, Risk: Medium — triggers 2-approver + CAB requirements.</t>
+          <t>Log records 'approval OK — CHG-2026-0912 approved by marcus.bell at 2026-06-28T14:47:00Z (self-approved)', confirming the deployer/approver/requester are the same individual.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Pre-deployment testing is completed and evidence retained before release</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1182,41 +1181,41 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Requester and Approver sections</t>
+          <t>Category / Testing evidence sections</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Both requester and approver are listed as 'Marcus Bell (Platform Engineer) — marcus.bell@northpeakfinancial.com' — same human, violating four-eyes.</t>
+          <t>Change is categorized 'Normal'; the Testing evidence section states '3 test cases failed on staging (2 functional, 1 performance). Deployment proceeded pending post-deployment fix.'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Pre-deployment testing is completed and evidence retained before release</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>pre-deployment-test-results.xlsx</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Approval record section</t>
+          <t>Test Cases!Result column (TC-002, TC-004)</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>CAB meeting reference '(none — deployed under standing team autonomy waiver)'; Approval decision 'Self-approved'; note states CAB was skipped to hit demo deadline and retroactive CAB scheduled for 2026-07-02.</t>
+          <t>TC-002 (Functional — Q2 aggregate) result FAIL and TC-004 (Regression — legacy CSV columns) result FAIL, confirming failed tests among pre-deployment results.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Pre-deployment testing is completed and evidence retained before release</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -1226,100 +1225,12 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Line 2026-06-28 15:04:20 UTC approval verification</t>
+          <t>2026-06-28 15:19:41–15:20:00 UTC lines</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Log confirms 'approved by marcus.bell at 2026-06-28T14:47:00Z (self-approved)' — deployment proceeded on a self-approval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>pre-deployment-test-results.xlsx</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Test Cases!D2:D6 (Result column)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>TC-002 (functional, Q2 aggregate) = FAIL and TC-004 (regression, CSV columns) = FAIL; executed 2026-06-28 09:03 and 09:05 UTC by test-bot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>change-request.md</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>## Testing evidence section</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>States '3 test cases failed on staging (2 functional, 1 performance). Deployment proceeded pending post-deployment fix.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>deployment-log.txt</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Final line 2026-06-28 15:31:02 UTC</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>'CHG-2026-0912 complete — status: DEPLOYED (with known post-deploy defects to be fixed 2026-06-29)' — confirms deployment proceeded despite failed pre-deployment tests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>pre-deployment-test-results.xlsx</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Test Cases!F2:F6 (Executed At)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>All test executions dated 2026-06-28 09:02–09:06 UTC, i.e. before deployment window start of 15:04 UTC — dating criterion met.</t>
+          <t>Two canary transactions FAILED (5xx), then 'override applied — accepting canary failure for demo'; deployment completed with status DEPLOYED despite failures.</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1303,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>change-request-documented, change-request-documented, change-request-documented, change-request-documented, change-request-documented, authorised-approver-pre-deployment, authorised-approver-pre-deployment, authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
+          <t>change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, approved-by-authorised-approver-before-deployment, approved-by-authorised-approver-before-deployment, pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1328,7 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>change-request-documented, authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
+          <t>change-request-documents-scope-risk-rollback, approved-by-authorised-approver-before-deployment, pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1353,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-testing-evidence, pre-deployment-testing-evidence</t>
+          <t>pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1524,33 +1435,33 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:40:38.512115Z</t>
+          <t>2026-07-03T04:15:27.645814Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documented:sample-1</t>
+          <t>judge:change-request-documents-scope-risk-rollback:sample-1</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>12237</v>
+        <v>3704</v>
       </c>
       <c r="F2" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>1427</v>
+      </c>
+      <c r="H2" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="16" t="n">
-        <v>3945</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>0.47943</v>
-      </c>
       <c r="I2" s="16" t="n">
-        <v>16903</v>
+        <v>16785</v>
       </c>
     </row>
     <row r="3">
@@ -1559,33 +1470,33 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:41:38.676590Z</t>
+          <t>2026-07-03T04:15:41.510267Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-pre-deployment:sample-1</t>
+          <t>judge:approved-by-authorised-approver-before-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>12282</v>
+        <v>3732</v>
       </c>
       <c r="F3" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="16" t="n">
-        <v>3635</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0.456855</v>
-      </c>
       <c r="I3" s="16" t="n">
-        <v>15711</v>
+        <v>13863</v>
       </c>
     </row>
     <row r="4">
@@ -1594,33 +1505,33 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:42:20.425037Z</t>
+          <t>2026-07-03T04:15:54.852178Z</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>judge:pre-deployment-testing-evidence:sample-1</t>
+          <t>judge:pre-deployment-testing-completed-evidence-retained:sample-1</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>12171</v>
+        <v>3681</v>
       </c>
       <c r="F4" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="16" t="n">
-        <v>3288</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.429165</v>
-      </c>
       <c r="I4" s="16" t="n">
-        <v>14789</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="5">
@@ -1629,33 +1540,33 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:43:34.856033Z</t>
+          <t>2026-07-03T04:16:10.922021Z</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documented:sample-2</t>
+          <t>judge:change-request-documents-scope-risk-rollback:sample-2</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>11808</v>
+        <v>3561</v>
       </c>
       <c r="F5" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>1373</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="16" t="n">
-        <v>3732</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.45702</v>
-      </c>
       <c r="I5" s="16" t="n">
-        <v>16764</v>
+        <v>16054</v>
       </c>
     </row>
     <row r="6">
@@ -1664,33 +1575,33 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:44:17.557054Z</t>
+          <t>2026-07-03T04:16:23.637445Z</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-pre-deployment:sample-2</t>
+          <t>judge:approved-by-authorised-approver-before-deployment:sample-2</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>11853</v>
+        <v>3589</v>
       </c>
       <c r="F6" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>1115</v>
+      </c>
+      <c r="H6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="16" t="n">
-        <v>3339</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.42822</v>
-      </c>
       <c r="I6" s="16" t="n">
-        <v>16002</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="7">
@@ -1699,33 +1610,33 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:49:13.305734Z</t>
+          <t>2026-07-03T04:16:36.533739Z</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>judge:pre-deployment-testing-evidence:sample-2</t>
+          <t>judge:pre-deployment-testing-completed-evidence-retained:sample-2</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>11742</v>
+        <v>3538</v>
       </c>
       <c r="F7" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>1089</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="16" t="n">
-        <v>3528</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.44073</v>
-      </c>
       <c r="I7" s="16" t="n">
-        <v>264910</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="8">
